--- a/artfynd/A 28519-2022 artfynd.xlsx
+++ b/artfynd/A 28519-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28519-2022 artfynd.xlsx
+++ b/artfynd/A 28519-2022 artfynd.xlsx
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121142866</v>
+        <v>121142869</v>
       </c>
       <c r="B7" t="n">
-        <v>4766</v>
+        <v>57504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,36 +1243,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480241</v>
+        <v>480287</v>
       </c>
       <c r="R7" t="n">
-        <v>6540019</v>
+        <v>6540066</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,18 +1317,12 @@
           <t>2023-10-17</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1348,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121142869</v>
+        <v>121142866</v>
       </c>
       <c r="B8" t="n">
-        <v>57501</v>
+        <v>4766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,35 +1353,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480287</v>
+        <v>480241</v>
       </c>
       <c r="R8" t="n">
-        <v>6540066</v>
+        <v>6540019</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,12 +1428,18 @@
           <t>2023-10-17</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121142867</v>
+        <v>121142868</v>
       </c>
       <c r="B9" t="n">
-        <v>5189</v>
+        <v>57367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,20 +1470,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1491,15 +1491,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1507,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480273</v>
+        <v>480275</v>
       </c>
       <c r="R9" t="n">
-        <v>6540033</v>
+        <v>6540038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,18 +1544,12 @@
           <t>2023-10-17</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121142868</v>
+        <v>121142867</v>
       </c>
       <c r="B10" t="n">
-        <v>57364</v>
+        <v>5189</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,20 +1580,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1608,14 +1601,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1623,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480275</v>
+        <v>480273</v>
       </c>
       <c r="R10" t="n">
-        <v>6540038</v>
+        <v>6540033</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,12 +1655,18 @@
           <t>2023-10-17</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28519-2022 artfynd.xlsx
+++ b/artfynd/A 28519-2022 artfynd.xlsx
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121142868</v>
+        <v>121142867</v>
       </c>
       <c r="B9" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,20 +1470,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1491,14 +1491,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1506,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480275</v>
+        <v>480273</v>
       </c>
       <c r="R9" t="n">
-        <v>6540038</v>
+        <v>6540033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,12 +1545,18 @@
           <t>2023-10-17</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1568,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121142867</v>
+        <v>121142868</v>
       </c>
       <c r="B10" t="n">
-        <v>5189</v>
+        <v>57367</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,20 +1587,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1601,15 +1608,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1617,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480273</v>
+        <v>480275</v>
       </c>
       <c r="R10" t="n">
-        <v>6540033</v>
+        <v>6540038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,18 +1661,12 @@
           <t>2023-10-17</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28519-2022 artfynd.xlsx
+++ b/artfynd/A 28519-2022 artfynd.xlsx
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121142867</v>
+        <v>121142868</v>
       </c>
       <c r="B9" t="n">
-        <v>5189</v>
+        <v>57367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,20 +1470,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1491,15 +1491,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1507,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480273</v>
+        <v>480275</v>
       </c>
       <c r="R9" t="n">
-        <v>6540033</v>
+        <v>6540038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,18 +1544,12 @@
           <t>2023-10-17</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121142868</v>
+        <v>121142867</v>
       </c>
       <c r="B10" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,20 +1580,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1608,14 +1601,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1623,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480275</v>
+        <v>480273</v>
       </c>
       <c r="R10" t="n">
-        <v>6540038</v>
+        <v>6540033</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,12 +1655,18 @@
           <t>2023-10-17</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28519-2022 artfynd.xlsx
+++ b/artfynd/A 28519-2022 artfynd.xlsx
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121142869</v>
+        <v>121142866</v>
       </c>
       <c r="B7" t="n">
-        <v>57504</v>
+        <v>4766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,35 +1243,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1279,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480287</v>
+        <v>480241</v>
       </c>
       <c r="R7" t="n">
-        <v>6540066</v>
+        <v>6540019</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,12 +1318,18 @@
           <t>2023-10-17</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1341,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121142866</v>
+        <v>121142868</v>
       </c>
       <c r="B8" t="n">
-        <v>4766</v>
+        <v>57367</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,36 +1360,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1390,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480241</v>
+        <v>480275</v>
       </c>
       <c r="R8" t="n">
-        <v>6540019</v>
+        <v>6540038</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,18 +1434,12 @@
           <t>2023-10-17</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121142868</v>
+        <v>121142867</v>
       </c>
       <c r="B9" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,20 +1470,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1491,14 +1491,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1506,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480275</v>
+        <v>480273</v>
       </c>
       <c r="R9" t="n">
-        <v>6540038</v>
+        <v>6540033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,12 +1545,18 @@
           <t>2023-10-17</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1568,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121142867</v>
+        <v>121142869</v>
       </c>
       <c r="B10" t="n">
-        <v>5189</v>
+        <v>57504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,36 +1587,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1617,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480273</v>
+        <v>480287</v>
       </c>
       <c r="R10" t="n">
-        <v>6540033</v>
+        <v>6540066</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,18 +1661,12 @@
           <t>2023-10-17</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28519-2022 artfynd.xlsx
+++ b/artfynd/A 28519-2022 artfynd.xlsx
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121142866</v>
+        <v>121142868</v>
       </c>
       <c r="B7" t="n">
-        <v>4766</v>
+        <v>57367</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,36 +1243,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480241</v>
+        <v>480275</v>
       </c>
       <c r="R7" t="n">
-        <v>6540019</v>
+        <v>6540038</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,18 +1317,12 @@
           <t>2023-10-17</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1348,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121142868</v>
+        <v>121142867</v>
       </c>
       <c r="B8" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,20 +1353,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1381,14 +1374,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480275</v>
+        <v>480273</v>
       </c>
       <c r="R8" t="n">
-        <v>6540038</v>
+        <v>6540033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,12 +1428,18 @@
           <t>2023-10-17</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121142867</v>
+        <v>121142866</v>
       </c>
       <c r="B9" t="n">
-        <v>5189</v>
+        <v>4766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,21 +1474,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480273</v>
+        <v>480241</v>
       </c>
       <c r="R9" t="n">
-        <v>6540033</v>
+        <v>6540019</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 28519-2022 artfynd.xlsx
+++ b/artfynd/A 28519-2022 artfynd.xlsx
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121142866</v>
+        <v>121142869</v>
       </c>
       <c r="B9" t="n">
-        <v>4766</v>
+        <v>57504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,36 +1470,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1507,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480241</v>
+        <v>480287</v>
       </c>
       <c r="R9" t="n">
-        <v>6540019</v>
+        <v>6540066</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,18 +1544,12 @@
           <t>2023-10-17</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121142869</v>
+        <v>121142866</v>
       </c>
       <c r="B10" t="n">
-        <v>57504</v>
+        <v>4766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,35 +1580,36 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1623,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480287</v>
+        <v>480241</v>
       </c>
       <c r="R10" t="n">
-        <v>6540066</v>
+        <v>6540019</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,12 +1655,18 @@
           <t>2023-10-17</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28519-2022 artfynd.xlsx
+++ b/artfynd/A 28519-2022 artfynd.xlsx
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121142868</v>
+        <v>121142869</v>
       </c>
       <c r="B7" t="n">
-        <v>57367</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,21 +1247,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480275</v>
+        <v>480287</v>
       </c>
       <c r="R7" t="n">
-        <v>6540038</v>
+        <v>6540066</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
         <v>121142867</v>
       </c>
       <c r="B8" t="n">
-        <v>5189</v>
+        <v>5192</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121142869</v>
+        <v>121142868</v>
       </c>
       <c r="B9" t="n">
-        <v>57504</v>
+        <v>57370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,21 +1474,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480287</v>
+        <v>480275</v>
       </c>
       <c r="R9" t="n">
-        <v>6540066</v>
+        <v>6540038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1571,7 @@
         <v>121142866</v>
       </c>
       <c r="B10" t="n">
-        <v>4766</v>
+        <v>4769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 28519-2022 artfynd.xlsx
+++ b/artfynd/A 28519-2022 artfynd.xlsx
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121142869</v>
+        <v>121142868</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,21 +1247,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480287</v>
+        <v>480275</v>
       </c>
       <c r="R7" t="n">
-        <v>6540066</v>
+        <v>6540038</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121142867</v>
+        <v>121142866</v>
       </c>
       <c r="B8" t="n">
-        <v>5192</v>
+        <v>4769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480273</v>
+        <v>480241</v>
       </c>
       <c r="R8" t="n">
-        <v>6540033</v>
+        <v>6540019</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121142868</v>
+        <v>121142869</v>
       </c>
       <c r="B9" t="n">
-        <v>57370</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,21 +1474,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480275</v>
+        <v>480287</v>
       </c>
       <c r="R9" t="n">
-        <v>6540038</v>
+        <v>6540066</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121142866</v>
+        <v>121142867</v>
       </c>
       <c r="B10" t="n">
-        <v>4769</v>
+        <v>5192</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,21 +1584,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480241</v>
+        <v>480273</v>
       </c>
       <c r="R10" t="n">
-        <v>6540019</v>
+        <v>6540033</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
